--- a/data/energy_dataset.csv.xlsx
+++ b/data/energy_dataset.csv.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\INFOSYS VIRTUAL INTERNSHIP 7.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\INFOSYS VIRTUAL INTERNSHIP 7.0\Agentic-AI-for-Smart-Facility-Operations-and-Optimization\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AB20DD1D-CD9A-48F9-A14F-1C552A1C2637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A35F387-7758-49AB-8662-878F0911A8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75CDF0D3-6C95-4D14-ABB8-A4E2399E651E}"/>
   </bookViews>
@@ -923,7 +923,16 @@
   <dimension ref="A1:J1001"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" customWidth="1"/>
+    <col min="7" max="7" width="19.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">

--- a/data/energy_dataset.csv.xlsx
+++ b/data/energy_dataset.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\INFOSYS VIRTUAL INTERNSHIP 7.0\Agentic-AI-for-Smart-Facility-Operations-and-Optimization\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A35F387-7758-49AB-8662-878F0911A8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE134E32-D923-4AFB-9DAC-BA8ABDBBCF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75CDF0D3-6C95-4D14-ABB8-A4E2399E651E}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{75CDF0D3-6C95-4D14-ABB8-A4E2399E651E}"/>
   </bookViews>
   <sheets>
     <sheet name="energy_agent_dataset_1000_recor" sheetId="1" r:id="rId1"/>
